--- a/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$123</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4231" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4566" uniqueCount="626">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:13:23+00:00</t>
+    <t>2026-06-19T14:20:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|1.2.0-snapshot-1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -394,7 +394,7 @@
     <t>as-ext-data-trace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -496,7 +496,7 @@
     <t>fr-canonical</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner-role|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner-role|2.2.0</t>
   </si>
   <si>
     <t>PractitionerRole.meta.profile:as-dr-canonical</t>
@@ -505,7 +505,7 @@
     <t>as-dr-canonical</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dr-practitionerrole|1.2.0-snapshot-1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dr-practitionerrole|1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>PractitionerRole.meta.security</t>
@@ -673,14 +673,16 @@
     <t>serviceTypeDuration</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-service-type-duration|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-service-type-duration|2.2.0}
 </t>
   </si>
   <si>
     <t>FR Core Service Type Duration Extension</t>
   </si>
   <si>
-    <t>This French extension allows to associate the type of service with the duration of this service | Cette extension française permet d'associer le type de service avec la durée de ce service.</t>
+    <t>Cette extension française permet d'associer le type de service avec la durée de ce service.
++This French extension allows to associate the type of service with the duration of this service</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -693,7 +695,7 @@
     <t>as-ext-practitionerrole-contracted</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-contracted|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-contracted|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -709,7 +711,7 @@
     <t>as-ext-practitionerrole-hascas</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-hascas|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-hascas|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -725,7 +727,7 @@
     <t>as-ext-practitionerrole-vitale-accepted</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-vitale-accepted|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-vitale-accepted|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -786,28 +788,28 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:idSituationExercice</t>
-  </si>
-  <si>
-    <t>idSituationExercice</t>
-  </si>
-  <si>
-    <t>Identifiant d'activité propre au RPPS</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier:idSituationExercice.id</t>
+    <t>PractitionerRole.identifier:numeroAm</t>
+  </si>
+  <si>
+    <t>numeroAm</t>
+  </si>
+  <si>
+    <t>Identifiant d’activité propre à l’Assurance Maladie. format: 9 digits. synonyme: numeroAM</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:numeroAm.id</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.id</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:idSituationExercice.extension</t>
+    <t>PractitionerRole.identifier:numeroAm.extension</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.extension</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:idSituationExercice.use</t>
+    <t>PractitionerRole.identifier:numeroAm.use</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.use</t>
@@ -840,7 +842,7 @@
     <t>Role.code or implied by context</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:idSituationExercice.type</t>
+    <t>PractitionerRole.identifier:numeroAm.type</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.type</t>
@@ -874,7 +876,7 @@
     <t>CX.5</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:idSituationExercice.system</t>
+    <t>PractitionerRole.identifier:numeroAm.system</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.system</t>
@@ -892,7 +894,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>https://rpps.esante.gouv.fr</t>
+    <t>https://www.ameli.fr</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -910,7 +912,7 @@
     <t>./IdentifierType</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:idSituationExercice.value</t>
+    <t>PractitionerRole.identifier:numeroAm.value</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.value</t>
@@ -940,7 +942,7 @@
     <t>./Value</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:idSituationExercice.period</t>
+    <t>PractitionerRole.identifier:numeroAm.period</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.period</t>
@@ -968,7 +970,7 @@
     <t>./StartDate and ./EndDate</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:idSituationExercice.assigner</t>
+    <t>PractitionerRole.identifier:numeroAm.assigner</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.assigner</t>
@@ -999,6 +1001,42 @@
     <t>./IdentifierIssuingAuthority</t>
   </si>
   <si>
+    <t>PractitionerRole.identifier:idSituationExercice</t>
+  </si>
+  <si>
+    <t>idSituationExercice</t>
+  </si>
+  <si>
+    <t>Identifiant d'activité propre au RPPS</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.use</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.type</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.system</t>
+  </si>
+  <si>
+    <t>https://rpps.esante.gouv.fr</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.value</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.period</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.assigner</t>
+  </si>
+  <si>
     <t>PractitionerRole.active</t>
   </si>
   <si>
@@ -1123,7 +1161,7 @@
     <t>PractitionerRole.practitioner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-2)
 </t>
   </si>
   <si>
@@ -1139,7 +1177,7 @@
     <t>PractitionerRole.organization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-2)
 </t>
   </si>
   <si>
@@ -1167,7 +1205,7 @@
     <t>Need to know what authority the practitioner has - what can they do?</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-role-exercice|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-role-exercice|2.2.0</t>
   </si>
   <si>
     <t>PRD-1 / STF-18  / PRA-3  / PRT-4  / ROL-3 / ORC-12 / OBR-16 / PV1-7 / PV1-8 / PV1-9 / PV1-17</t>
@@ -1290,7 +1328,7 @@
     <t>Specific specialty of the practitioner.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty|2.2.0</t>
   </si>
   <si>
     <t>PRA-5</t>
@@ -1305,7 +1343,7 @@
     <t>PractitionerRole.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.1.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0)
 </t>
   </si>
   <si>
@@ -1327,7 +1365,7 @@
     <t>PractitionerRole.healthcareService</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-healthcare-service|2.1.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-healthcare-service|2.2.0)
 </t>
   </si>
   <si>
@@ -1346,14 +1384,14 @@
     <t>PractitionerRole.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.1.0}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0}
 </t>
   </si>
   <si>
     <t>Details of a Technology mediated contact point | Coordonnées électroniques détaillées</t>
   </si>
   <si>
-    <t>Details for all kinds of technology mediated contact points for a person or organization, including telephone, email, etc.</t>
+    <t>Contact details that are specific to the role/location/service.</t>
   </si>
   <si>
     <t>Often practitioners have a dedicated line for each location (or service) that they work at, and need to be able to define separate contact details for each of these.</t>
@@ -1363,20 +1401,10 @@
 exists:extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type')}</t>
   </si>
   <si>
-    <t>cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}
-ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
-  </si>
-  <si>
     <t>SituationExercice.telecommunication</t>
   </si>
   <si>
-    <t>XTN</t>
-  </si>
-  <si>
-    <t>TEL</t>
-  </si>
-  <si>
-    <t>ContactPoint</t>
+    <t>.telecom</t>
   </si>
   <si>
     <t>PractitionerRole.telecom:mailbox-mss</t>
@@ -1385,7 +1413,7 @@
     <t>mailbox-mss</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-1}
+    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -1413,14 +1441,16 @@
     <t>emailType</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type|2.2.0}
 </t>
   </si>
   <si>
     <t>Type of email | type de messagerie électronique</t>
   </si>
   <si>
-    <t>Extension on the ContactPoint datatype. This extension allows to specify the type of mail used to contact the person (MSSsanté|Apicrypt|OSM|Autre).</t>
+    <t>Extension permettant d'indiquer le type d'adresse email d'un ContactPoint.
++ This extension allows to specify the type of mail used to contact the person.</t>
   </si>
   <si>
     <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.id</t>
@@ -1474,7 +1504,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-email-type|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-email-type|2.2.0</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -1486,7 +1516,7 @@
     <t>as-mailbox-mss-metadata</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -2244,7 +2274,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO114"/>
+  <dimension ref="A1:AO123"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="86.015625" customWidth="true" bestFit="true"/>
@@ -6392,14 +6422,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>316</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="D36" t="s" s="2">
         <v>78</v>
       </c>
@@ -6411,7 +6443,7 @@
         <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>78</v>
@@ -6420,26 +6452,22 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>317</v>
+        <v>236</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>318</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>321</v>
+        <v>239</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q36" t="s" s="2">
-        <v>322</v>
-      </c>
+      <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
         <v>78</v>
       </c>
@@ -6483,13 +6511,13 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>316</v>
+        <v>235</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>78</v>
@@ -6501,24 +6529,24 @@
         <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>323</v>
+        <v>242</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>324</v>
+        <v>243</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>78</v>
+        <v>244</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>325</v>
+        <v>245</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>326</v>
+        <v>250</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6532,27 +6560,25 @@
         <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>299</v>
+        <v>104</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>327</v>
+        <v>105</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>328</v>
+        <v>106</v>
       </c>
       <c r="N37" s="2"/>
-      <c r="O37" t="s" s="2">
-        <v>329</v>
-      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>78</v>
       </c>
@@ -6600,7 +6626,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>326</v>
+        <v>107</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6612,41 +6638,41 @@
         <v>78</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>330</v>
+        <v>78</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>331</v>
+        <v>108</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>332</v>
+        <v>78</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>333</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>334</v>
+        <v>252</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>78</v>
@@ -6658,15 +6684,17 @@
         <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -6703,31 +6731,31 @@
         <v>78</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>78</v>
@@ -6747,44 +6775,46 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>335</v>
+        <v>254</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>111</v>
+        <v>181</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>112</v>
+        <v>255</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>113</v>
+        <v>256</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
       </c>
@@ -6808,52 +6838,52 @@
         <v>78</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>78</v>
+        <v>259</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>78</v>
+        <v>260</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>78</v>
+        <v>261</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>118</v>
+        <v>262</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>78</v>
+        <v>204</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>108</v>
+        <v>263</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>
@@ -6864,10 +6894,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>336</v>
+        <v>265</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6890,18 +6920,20 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>337</v>
+        <v>266</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>338</v>
+        <v>267</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>339</v>
+        <v>268</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>78</v>
       </c>
@@ -6925,13 +6957,13 @@
         <v>78</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>78</v>
+        <v>163</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>78</v>
+        <v>271</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>78</v>
+        <v>272</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>78</v>
@@ -6949,7 +6981,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>341</v>
+        <v>273</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6958,19 +6990,19 @@
         <v>90</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>342</v>
+        <v>78</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>343</v>
+        <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>344</v>
+        <v>274</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>345</v>
+        <v>263</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
@@ -6981,10 +7013,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>346</v>
+        <v>323</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>346</v>
+        <v>276</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6992,7 +7024,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>90</v>
@@ -7007,32 +7039,32 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>337</v>
+        <v>137</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>347</v>
+        <v>277</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>348</v>
+        <v>278</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q41" t="s" s="2">
-        <v>350</v>
-      </c>
+      <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>78</v>
+        <v>324</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>78</v>
+        <v>282</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>78</v>
@@ -7068,7 +7100,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>351</v>
+        <v>283</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7077,33 +7109,33 @@
         <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>342</v>
+        <v>78</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>352</v>
+        <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>353</v>
+        <v>284</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>354</v>
+        <v>285</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>78</v>
+        <v>286</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>355</v>
+        <v>325</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>355</v>
+        <v>288</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7111,13 +7143,13 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>78</v>
@@ -7126,15 +7158,17 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>356</v>
+        <v>104</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>357</v>
+        <v>289</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -7147,7 +7181,7 @@
         <v>78</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>78</v>
+        <v>292</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>78</v>
@@ -7183,7 +7217,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>355</v>
+        <v>293</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7201,24 +7235,24 @@
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>78</v>
+        <v>294</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>359</v>
+        <v>295</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>78</v>
+        <v>296</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>360</v>
+        <v>326</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>360</v>
+        <v>298</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7232,7 +7266,7 @@
         <v>90</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>78</v>
@@ -7241,13 +7275,13 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>361</v>
+        <v>299</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>362</v>
+        <v>300</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>363</v>
+        <v>301</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7298,7 +7332,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>360</v>
+        <v>302</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7316,13 +7350,13 @@
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>78</v>
+        <v>303</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>364</v>
+        <v>304</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>78</v>
+        <v>305</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>78</v>
@@ -7330,10 +7364,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>365</v>
+        <v>327</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>365</v>
+        <v>307</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7344,7 +7378,7 @@
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>78</v>
@@ -7356,20 +7390,18 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>266</v>
+        <v>308</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>366</v>
+        <v>309</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>367</v>
+        <v>310</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>369</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>78</v>
       </c>
@@ -7393,33 +7425,37 @@
         <v>78</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z44" t="s" s="2">
-        <v>370</v>
+        <v>78</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="AC44" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>365</v>
+        <v>312</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>78</v>
@@ -7431,13 +7467,13 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>371</v>
+        <v>313</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>372</v>
+        <v>314</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>78</v>
@@ -7445,14 +7481,12 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>373</v>
+        <v>328</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>374</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>78</v>
       </c>
@@ -7473,24 +7507,26 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>266</v>
+        <v>329</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>375</v>
+        <v>330</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>367</v>
+        <v>331</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>368</v>
+        <v>332</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>369</v>
+        <v>333</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q45" s="2"/>
+      <c r="Q45" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="R45" t="s" s="2">
         <v>78</v>
       </c>
@@ -7510,11 +7546,13 @@
         <v>78</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="Y45" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z45" t="s" s="2">
-        <v>376</v>
+        <v>78</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>78</v>
@@ -7532,13 +7570,13 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>365</v>
+        <v>328</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>78</v>
@@ -7547,31 +7585,29 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>377</v>
+        <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>371</v>
+        <v>335</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>372</v>
+        <v>336</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>332</v>
+        <v>78</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>78</v>
+        <v>337</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>378</v>
+        <v>338</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>78</v>
       </c>
@@ -7592,19 +7628,17 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>266</v>
+        <v>299</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>380</v>
+        <v>339</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>369</v>
+        <v>341</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
@@ -7629,11 +7663,13 @@
         <v>78</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="Y46" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z46" t="s" s="2">
-        <v>381</v>
+        <v>78</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>78</v>
@@ -7651,13 +7687,13 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>365</v>
+        <v>338</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>78</v>
@@ -7666,31 +7702,29 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>382</v>
+        <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>371</v>
+        <v>342</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>78</v>
+        <v>345</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>383</v>
+        <v>346</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>384</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>78</v>
       </c>
@@ -7702,29 +7736,25 @@
         <v>90</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>266</v>
+        <v>104</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>385</v>
+        <v>105</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>369</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>78</v>
       </c>
@@ -7748,11 +7778,13 @@
         <v>78</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="Y47" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z47" t="s" s="2">
-        <v>386</v>
+        <v>78</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>78</v>
@@ -7770,80 +7802,76 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>365</v>
+        <v>107</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>387</v>
+        <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>371</v>
+        <v>78</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>372</v>
+        <v>108</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>332</v>
+        <v>78</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>388</v>
+        <v>347</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>389</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>266</v>
+        <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>390</v>
+        <v>112</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>367</v>
+        <v>113</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>369</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>78</v>
       </c>
@@ -7867,29 +7895,31 @@
         <v>78</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="Y48" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z48" t="s" s="2">
-        <v>391</v>
+        <v>78</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>365</v>
+        <v>118</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7901,34 +7931,32 @@
         <v>78</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>392</v>
+        <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>371</v>
+        <v>78</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>372</v>
+        <v>108</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>332</v>
+        <v>78</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>393</v>
+        <v>348</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>394</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>78</v>
       </c>
@@ -7940,7 +7968,7 @@
         <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>78</v>
@@ -7949,20 +7977,18 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>266</v>
+        <v>349</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>395</v>
+        <v>350</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>369</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>78</v>
       </c>
@@ -7986,11 +8012,13 @@
         <v>78</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="Y49" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z49" t="s" s="2">
-        <v>396</v>
+        <v>78</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>78</v>
@@ -8008,46 +8036,44 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>78</v>
+        <v>354</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>397</v>
+        <v>355</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>332</v>
+        <v>78</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>398</v>
+        <v>358</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="C50" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>78</v>
       </c>
@@ -8059,7 +8085,7 @@
         <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>78</v>
@@ -8068,24 +8094,24 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>266</v>
+        <v>349</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>400</v>
+        <v>359</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>369</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q50" s="2"/>
+      <c r="Q50" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="R50" t="s" s="2">
         <v>78</v>
       </c>
@@ -8105,11 +8131,13 @@
         <v>78</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="Y50" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z50" t="s" s="2">
-        <v>401</v>
+        <v>78</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>78</v>
@@ -8127,31 +8155,31 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>78</v>
+        <v>354</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>402</v>
+        <v>364</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>332</v>
+        <v>78</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>78</v>
@@ -8159,23 +8187,21 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>403</v>
+        <v>367</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>91</v>
@@ -8187,20 +8213,16 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>266</v>
+        <v>368</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>405</v>
+        <v>369</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>369</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>78</v>
       </c>
@@ -8224,11 +8246,13 @@
         <v>78</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="Y51" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>406</v>
+        <v>78</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>78</v>
@@ -8246,13 +8270,13 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>78</v>
@@ -8261,27 +8285,27 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>407</v>
+        <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AN51" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="52" hidden="true">
-      <c r="A52" t="s" s="2">
-        <v>408</v>
-      </c>
       <c r="B52" t="s" s="2">
-        <v>408</v>
+        <v>372</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8292,10 +8316,10 @@
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>78</v>
@@ -8304,13 +8328,13 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>266</v>
+        <v>373</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>409</v>
+        <v>374</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>410</v>
+        <v>375</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8337,11 +8361,13 @@
         <v>78</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="Y52" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z52" t="s" s="2">
-        <v>411</v>
+        <v>78</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>78</v>
@@ -8359,13 +8385,13 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>408</v>
+        <v>372</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>78</v>
@@ -8377,13 +8403,13 @@
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>412</v>
+        <v>78</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>413</v>
+        <v>376</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>414</v>
+        <v>78</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>78</v>
@@ -8391,10 +8417,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>415</v>
+        <v>377</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>415</v>
+        <v>377</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8417,16 +8443,20 @@
         <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>416</v>
+        <v>266</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>417</v>
+        <v>378</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
       </c>
@@ -8450,31 +8480,27 @@
         <v>78</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>78</v>
+        <v>382</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>415</v>
+        <v>377</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8492,26 +8518,28 @@
         <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>78</v>
+        <v>383</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>419</v>
+        <v>384</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>420</v>
+        <v>344</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>421</v>
+        <v>78</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>422</v>
+        <v>385</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="C54" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="D54" t="s" s="2">
         <v>78</v>
       </c>
@@ -8520,7 +8548,7 @@
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>91</v>
@@ -8529,19 +8557,23 @@
         <v>78</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>423</v>
+        <v>266</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>424</v>
+        <v>387</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
       </c>
@@ -8565,13 +8597,11 @@
         <v>78</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>78</v>
+        <v>388</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8589,7 +8619,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>422</v>
+        <v>377</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8604,29 +8634,31 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>426</v>
+        <v>383</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>427</v>
+        <v>384</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>78</v>
+        <v>344</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>428</v>
+        <v>390</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="C55" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="D55" t="s" s="2">
         <v>78</v>
       </c>
@@ -8635,7 +8667,7 @@
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>91</v>
@@ -8644,20 +8676,22 @@
         <v>78</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>429</v>
+        <v>266</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>430</v>
+        <v>392</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="O55" t="s" s="2">
-        <v>432</v>
+        <v>381</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8682,29 +8716,29 @@
         <v>78</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>78</v>
+        <v>393</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AC55" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>428</v>
+        <v>377</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8713,36 +8747,36 @@
         <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>214</v>
+        <v>78</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>434</v>
+        <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>435</v>
+        <v>394</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>436</v>
+        <v>383</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>437</v>
+        <v>384</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>438</v>
+        <v>344</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>439</v>
+        <v>395</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>428</v>
+        <v>377</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>440</v>
+        <v>396</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>78</v>
@@ -8752,29 +8786,31 @@
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>441</v>
+        <v>266</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>442</v>
+        <v>397</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="O56" t="s" s="2">
-        <v>432</v>
+        <v>381</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8799,13 +8835,11 @@
         <v>78</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>78</v>
+        <v>398</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>78</v>
@@ -8823,7 +8857,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>428</v>
+        <v>377</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8832,35 +8866,37 @@
         <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>214</v>
+        <v>78</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>434</v>
+        <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>443</v>
+        <v>399</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>436</v>
+        <v>383</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>437</v>
+        <v>384</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>438</v>
+        <v>344</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>444</v>
+        <v>400</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="C57" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="D57" t="s" s="2">
         <v>78</v>
       </c>
@@ -8872,25 +8908,29 @@
         <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>104</v>
+        <v>266</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>105</v>
+        <v>402</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
       </c>
@@ -8914,13 +8954,11 @@
         <v>78</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>78</v>
+        <v>403</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>78</v>
@@ -8938,74 +8976,80 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>107</v>
+        <v>377</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>78</v>
+        <v>404</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>78</v>
+        <v>383</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>108</v>
+        <v>384</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>78</v>
+        <v>344</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>446</v>
+        <v>405</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C58" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="C58" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="D58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>111</v>
+        <v>266</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>206</v>
+        <v>407</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
       </c>
@@ -9029,31 +9073,29 @@
         <v>78</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>78</v>
+        <v>408</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>118</v>
+        <v>377</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9065,64 +9107,68 @@
         <v>78</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>78</v>
+        <v>409</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>78</v>
+        <v>383</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>78</v>
+        <v>384</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>78</v>
+        <v>344</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>448</v>
+        <v>410</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>447</v>
+        <v>377</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>449</v>
+        <v>411</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>450</v>
+        <v>266</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>451</v>
+        <v>412</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
       </c>
@@ -9146,13 +9192,11 @@
         <v>78</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>78</v>
+        <v>413</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>78</v>
@@ -9170,7 +9214,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>118</v>
+        <v>377</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9182,32 +9226,34 @@
         <v>78</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>78</v>
+        <v>414</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>78</v>
+        <v>383</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>78</v>
+        <v>384</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>78</v>
+        <v>344</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>453</v>
+        <v>415</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="C60" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>416</v>
+      </c>
       <c r="D60" t="s" s="2">
         <v>78</v>
       </c>
@@ -9216,28 +9262,32 @@
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>104</v>
+        <v>266</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>105</v>
+        <v>417</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
       </c>
@@ -9261,13 +9311,11 @@
         <v>78</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>78</v>
+        <v>418</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
@@ -9285,31 +9333,31 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>107</v>
+        <v>377</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>78</v>
+        <v>419</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>78</v>
+        <v>383</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>108</v>
+        <v>384</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>78</v>
+        <v>344</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>78</v>
@@ -9317,10 +9365,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>455</v>
+        <v>420</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>456</v>
+        <v>420</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9340,16 +9388,16 @@
         <v>78</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>111</v>
+        <v>266</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>206</v>
+        <v>421</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>207</v>
+        <v>422</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9376,31 +9424,29 @@
         <v>78</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>78</v>
+        <v>423</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>118</v>
+        <v>420</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9412,19 +9458,19 @@
         <v>78</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>78</v>
+        <v>424</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>78</v>
+        <v>425</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>78</v>
+        <v>426</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>78</v>
@@ -9432,10 +9478,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>457</v>
+        <v>427</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>458</v>
+        <v>427</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9443,10 +9489,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>78</v>
@@ -9455,27 +9501,25 @@
         <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>137</v>
+        <v>428</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>459</v>
+        <v>429</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>462</v>
+        <v>78</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>78</v>
@@ -9517,19 +9561,19 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>463</v>
+        <v>427</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>78</v>
@@ -9538,21 +9582,21 @@
         <v>78</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>204</v>
+        <v>431</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>78</v>
+        <v>432</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>78</v>
+        <v>433</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>464</v>
+        <v>434</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>465</v>
+        <v>434</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9563,10 +9607,10 @@
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>78</v>
@@ -9575,13 +9619,13 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>159</v>
+        <v>435</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>467</v>
+        <v>437</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9593,7 +9637,7 @@
         <v>78</v>
       </c>
       <c r="S63" t="s" s="2">
-        <v>468</v>
+        <v>78</v>
       </c>
       <c r="T63" t="s" s="2">
         <v>78</v>
@@ -9608,11 +9652,13 @@
         <v>78</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Y63" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z63" t="s" s="2">
-        <v>469</v>
+        <v>78</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>78</v>
@@ -9630,13 +9676,13 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>470</v>
+        <v>434</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>78</v>
@@ -9648,10 +9694,10 @@
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>78</v>
+        <v>438</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>204</v>
+        <v>439</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -9662,14 +9708,12 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>471</v>
+        <v>440</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>78</v>
       </c>
@@ -9678,28 +9722,30 @@
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>473</v>
+        <v>441</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>474</v>
+        <v>442</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>475</v>
+        <v>443</v>
       </c>
       <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
       </c>
@@ -9735,19 +9781,17 @@
         <v>78</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="AC64" s="2"/>
       <c r="AD64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>118</v>
+        <v>440</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9759,16 +9803,16 @@
         <v>78</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>78</v>
+        <v>446</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>78</v>
+        <v>447</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -9779,12 +9823,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>476</v>
+        <v>448</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="C65" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="D65" t="s" s="2">
         <v>78</v>
       </c>
@@ -9793,7 +9839,7 @@
         <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>78</v>
@@ -9802,19 +9848,21 @@
         <v>78</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>104</v>
+        <v>450</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>105</v>
+        <v>451</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>106</v>
+        <v>443</v>
       </c>
       <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>78</v>
       </c>
@@ -9862,28 +9910,28 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>107</v>
+        <v>440</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>78</v>
+        <v>452</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>108</v>
+        <v>447</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
@@ -9894,21 +9942,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>477</v>
+        <v>453</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>78</v>
@@ -9920,17 +9968,15 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -9967,31 +10013,31 @@
         <v>78</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
@@ -10011,23 +10057,21 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>478</v>
+        <v>455</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="C67" t="s" s="2">
-        <v>479</v>
-      </c>
+      <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>78</v>
@@ -10042,7 +10086,7 @@
         <v>111</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>480</v>
+        <v>206</v>
       </c>
       <c r="M67" t="s" s="2">
         <v>207</v>
@@ -10084,16 +10128,16 @@
         <v>78</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>118</v>
@@ -10128,18 +10172,20 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>481</v>
+        <v>457</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="C68" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>458</v>
+      </c>
       <c r="D68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>90</v>
@@ -10154,13 +10200,13 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>104</v>
+        <v>459</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>105</v>
+        <v>460</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>106</v>
+        <v>461</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10211,19 +10257,19 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>78</v>
@@ -10232,7 +10278,7 @@
         <v>78</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>78</v>
@@ -10243,10 +10289,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>483</v>
+        <v>462</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>484</v>
+        <v>463</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10257,7 +10303,7 @@
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>78</v>
@@ -10269,13 +10315,13 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>206</v>
+        <v>105</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>207</v>
+        <v>106</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10314,31 +10360,31 @@
         <v>78</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>78</v>
@@ -10347,7 +10393,7 @@
         <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>78</v>
@@ -10358,10 +10404,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>485</v>
+        <v>464</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>486</v>
+        <v>465</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10369,10 +10415,10 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>78</v>
@@ -10384,24 +10430,22 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>459</v>
+        <v>206</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>479</v>
+        <v>78</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>78</v>
@@ -10431,31 +10475,31 @@
         <v>78</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>463</v>
+        <v>118</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>78</v>
@@ -10464,7 +10508,7 @@
         <v>78</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>78</v>
@@ -10475,10 +10519,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>487</v>
+        <v>466</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>488</v>
+        <v>467</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10486,7 +10530,7 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>90</v>
@@ -10501,22 +10545,24 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>266</v>
+        <v>137</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>78</v>
+        <v>471</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>78</v>
@@ -10534,11 +10580,13 @@
         <v>78</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="Y71" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z71" t="s" s="2">
-        <v>489</v>
+        <v>78</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>78</v>
@@ -10556,10 +10604,10 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>90</v>
@@ -10568,7 +10616,7 @@
         <v>78</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>78</v>
@@ -10588,14 +10636,12 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>490</v>
+        <v>473</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="C72" t="s" s="2">
-        <v>491</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
         <v>78</v>
       </c>
@@ -10616,13 +10662,13 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>111</v>
+        <v>159</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>206</v>
+        <v>475</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>207</v>
+        <v>476</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10634,7 +10680,7 @@
         <v>78</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>78</v>
+        <v>477</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>78</v>
@@ -10649,13 +10695,11 @@
         <v>78</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>78</v>
+        <v>478</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>78</v>
@@ -10673,19 +10717,19 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>118</v>
+        <v>479</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>78</v>
@@ -10694,7 +10738,7 @@
         <v>78</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>78</v>
+        <v>204</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -10705,12 +10749,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="C73" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="C73" t="s" s="2">
+        <v>481</v>
+      </c>
       <c r="D73" t="s" s="2">
         <v>78</v>
       </c>
@@ -10731,13 +10777,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>104</v>
+        <v>482</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>105</v>
+        <v>483</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>106</v>
+        <v>484</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10788,19 +10834,19 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>78</v>
@@ -10809,7 +10855,7 @@
         <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10820,10 +10866,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>484</v>
+        <v>463</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10834,7 +10880,7 @@
         <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>78</v>
@@ -10846,13 +10892,13 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>206</v>
+        <v>105</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>207</v>
+        <v>106</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10891,31 +10937,31 @@
         <v>78</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>78</v>
@@ -10924,7 +10970,7 @@
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -10935,21 +10981,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>486</v>
+        <v>465</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>78</v>
@@ -10961,16 +11007,16 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>459</v>
+        <v>112</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>460</v>
+        <v>113</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>461</v>
+        <v>114</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10978,7 +11024,7 @@
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>491</v>
+        <v>78</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>78</v>
@@ -11008,31 +11054,31 @@
         <v>78</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>463</v>
+        <v>118</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>78</v>
@@ -11041,7 +11087,7 @@
         <v>78</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>204</v>
+        <v>108</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>78</v>
@@ -11052,12 +11098,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="B76" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="C76" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>78</v>
       </c>
@@ -11078,13 +11126,13 @@
         <v>78</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>466</v>
+        <v>489</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>467</v>
+        <v>207</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11135,19 +11183,19 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>470</v>
+        <v>118</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>78</v>
@@ -11156,7 +11204,7 @@
         <v>78</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>78</v>
@@ -11167,14 +11215,12 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>497</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>78</v>
       </c>
@@ -11195,13 +11241,13 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>498</v>
+        <v>105</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>207</v>
+        <v>106</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11252,19 +11298,19 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>78</v>
@@ -11273,7 +11319,7 @@
         <v>78</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>78</v>
@@ -11284,10 +11330,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11298,7 +11344,7 @@
         <v>79</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>78</v>
@@ -11310,13 +11356,13 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>105</v>
+        <v>206</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>106</v>
+        <v>207</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11355,31 +11401,31 @@
         <v>78</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>78</v>
@@ -11388,7 +11434,7 @@
         <v>78</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -11399,10 +11445,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11410,10 +11456,10 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>78</v>
@@ -11425,22 +11471,24 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>206</v>
+        <v>468</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>78</v>
+        <v>488</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>78</v>
@@ -11470,31 +11518,31 @@
         <v>78</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>118</v>
+        <v>472</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>78</v>
@@ -11503,7 +11551,7 @@
         <v>78</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>78</v>
+        <v>204</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
@@ -11514,10 +11562,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11525,7 +11573,7 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>90</v>
@@ -11540,24 +11588,22 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>137</v>
+        <v>266</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
-        <v>497</v>
+        <v>78</v>
       </c>
       <c r="S80" t="s" s="2">
         <v>78</v>
@@ -11575,13 +11621,11 @@
         <v>78</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>78</v>
+        <v>498</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>78</v>
@@ -11599,10 +11643,10 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>463</v>
+        <v>479</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>90</v>
@@ -11611,7 +11655,7 @@
         <v>78</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>78</v>
@@ -11631,12 +11675,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C81" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="C81" t="s" s="2">
+        <v>500</v>
+      </c>
       <c r="D81" t="s" s="2">
         <v>78</v>
       </c>
@@ -11657,13 +11703,13 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>466</v>
+        <v>206</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>467</v>
+        <v>207</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11714,19 +11760,19 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>470</v>
+        <v>118</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>78</v>
@@ -11735,7 +11781,7 @@
         <v>78</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
@@ -11746,14 +11792,12 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="C82" t="s" s="2">
-        <v>504</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
         <v>78</v>
       </c>
@@ -11774,13 +11818,13 @@
         <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>206</v>
+        <v>105</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>207</v>
+        <v>106</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11831,19 +11875,19 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>78</v>
@@ -11852,7 +11896,7 @@
         <v>78</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>78</v>
@@ -11863,10 +11907,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11877,7 +11921,7 @@
         <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>78</v>
@@ -11889,13 +11933,13 @@
         <v>78</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>105</v>
+        <v>206</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>106</v>
+        <v>207</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11934,31 +11978,31 @@
         <v>78</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>78</v>
@@ -11967,7 +12011,7 @@
         <v>78</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>78</v>
@@ -11978,10 +12022,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11989,10 +12033,10 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>78</v>
@@ -12004,22 +12048,24 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>206</v>
+        <v>468</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
-        <v>78</v>
+        <v>500</v>
       </c>
       <c r="S84" t="s" s="2">
         <v>78</v>
@@ -12049,31 +12095,31 @@
         <v>78</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>118</v>
+        <v>472</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>78</v>
@@ -12082,7 +12128,7 @@
         <v>78</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>78</v>
+        <v>204</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>78</v>
@@ -12093,10 +12139,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12104,7 +12150,7 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>90</v>
@@ -12119,24 +12165,22 @@
         <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
-        <v>504</v>
+        <v>78</v>
       </c>
       <c r="S85" t="s" s="2">
         <v>78</v>
@@ -12178,10 +12222,10 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>463</v>
+        <v>479</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>90</v>
@@ -12190,7 +12234,7 @@
         <v>78</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>78</v>
@@ -12210,12 +12254,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C86" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="C86" t="s" s="2">
+        <v>506</v>
+      </c>
       <c r="D86" t="s" s="2">
         <v>78</v>
       </c>
@@ -12236,13 +12282,13 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>466</v>
+        <v>507</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>467</v>
+        <v>207</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12293,19 +12339,19 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>470</v>
+        <v>118</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>78</v>
@@ -12314,7 +12360,7 @@
         <v>78</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>78</v>
@@ -12325,14 +12371,12 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="C87" t="s" s="2">
-        <v>510</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
         <v>78</v>
       </c>
@@ -12353,13 +12397,13 @@
         <v>78</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>206</v>
+        <v>105</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>207</v>
+        <v>106</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12410,19 +12454,19 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>78</v>
@@ -12431,7 +12475,7 @@
         <v>78</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>78</v>
@@ -12442,10 +12486,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12456,7 +12500,7 @@
         <v>79</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>78</v>
@@ -12468,13 +12512,13 @@
         <v>78</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>105</v>
+        <v>206</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>106</v>
+        <v>207</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12513,31 +12557,31 @@
         <v>78</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>78</v>
@@ -12546,7 +12590,7 @@
         <v>78</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>78</v>
@@ -12557,10 +12601,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12568,10 +12612,10 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>78</v>
@@ -12583,22 +12627,24 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>206</v>
+        <v>468</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q89" s="2"/>
       <c r="R89" t="s" s="2">
-        <v>78</v>
+        <v>506</v>
       </c>
       <c r="S89" t="s" s="2">
         <v>78</v>
@@ -12628,31 +12674,31 @@
         <v>78</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>118</v>
+        <v>472</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>78</v>
@@ -12661,7 +12707,7 @@
         <v>78</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>78</v>
+        <v>204</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>78</v>
@@ -12672,10 +12718,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12683,7 +12729,7 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>90</v>
@@ -12698,24 +12744,22 @@
         <v>78</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>510</v>
+        <v>78</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>78</v>
@@ -12757,10 +12801,10 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>463</v>
+        <v>479</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>90</v>
@@ -12769,7 +12813,7 @@
         <v>78</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>78</v>
@@ -12789,12 +12833,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C91" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="C91" t="s" s="2">
+        <v>513</v>
+      </c>
       <c r="D91" t="s" s="2">
         <v>78</v>
       </c>
@@ -12815,13 +12861,13 @@
         <v>78</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>317</v>
+        <v>111</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>466</v>
+        <v>206</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>467</v>
+        <v>207</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12872,19 +12918,19 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>470</v>
+        <v>118</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>78</v>
@@ -12893,7 +12939,7 @@
         <v>78</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>78</v>
@@ -12904,10 +12950,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>458</v>
+        <v>491</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12915,7 +12961,7 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>90</v>
@@ -12930,24 +12976,22 @@
         <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>459</v>
+        <v>105</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>516</v>
+        <v>78</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>78</v>
@@ -12989,10 +13033,10 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>463</v>
+        <v>107</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>90</v>
@@ -13010,7 +13054,7 @@
         <v>78</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>204</v>
+        <v>108</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>78</v>
@@ -13021,10 +13065,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13047,13 +13091,13 @@
         <v>78</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>518</v>
+        <v>111</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>466</v>
+        <v>206</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>467</v>
+        <v>207</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13092,31 +13136,31 @@
         <v>78</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>470</v>
+        <v>118</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>78</v>
@@ -13125,7 +13169,7 @@
         <v>78</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>78</v>
@@ -13136,10 +13180,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>520</v>
+        <v>495</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13159,28 +13203,30 @@
         <v>78</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>181</v>
+        <v>137</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>521</v>
+        <v>468</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N94" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q94" s="2"/>
       <c r="R94" t="s" s="2">
-        <v>78</v>
+        <v>513</v>
       </c>
       <c r="S94" t="s" s="2">
-        <v>523</v>
+        <v>78</v>
       </c>
       <c r="T94" t="s" s="2">
         <v>78</v>
@@ -13195,13 +13241,13 @@
         <v>78</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>259</v>
+        <v>78</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>524</v>
+        <v>78</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>525</v>
+        <v>78</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>78</v>
@@ -13219,42 +13265,42 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>526</v>
+        <v>472</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>527</v>
+        <v>78</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>528</v>
+        <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>529</v>
+        <v>78</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>530</v>
+        <v>204</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>531</v>
+        <v>78</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>532</v>
+        <v>517</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>533</v>
+        <v>497</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13262,35 +13308,31 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>534</v>
+        <v>475</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>537</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>78</v>
       </c>
@@ -13338,7 +13380,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>538</v>
+        <v>479</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13353,16 +13395,16 @@
         <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>539</v>
+        <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>540</v>
+        <v>78</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>541</v>
+        <v>204</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>296</v>
+        <v>78</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>78</v>
@@ -13370,12 +13412,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>542</v>
+        <v>518</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C96" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="C96" t="s" s="2">
+        <v>519</v>
+      </c>
       <c r="D96" t="s" s="2">
         <v>78</v>
       </c>
@@ -13390,26 +13434,22 @@
         <v>78</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>181</v>
+        <v>111</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>544</v>
+        <v>206</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>547</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>78</v>
       </c>
@@ -13433,13 +13473,13 @@
         <v>78</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>259</v>
+        <v>78</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>548</v>
+        <v>78</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>549</v>
+        <v>78</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>78</v>
@@ -13457,31 +13497,31 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>550</v>
+        <v>118</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>551</v>
+        <v>78</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>552</v>
+        <v>78</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>553</v>
+        <v>78</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>554</v>
+        <v>78</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>78</v>
@@ -13489,10 +13529,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>555</v>
+        <v>520</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>556</v>
+        <v>491</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13512,20 +13552,18 @@
         <v>78</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>557</v>
+        <v>104</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>558</v>
+        <v>105</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>560</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>78</v>
@@ -13574,7 +13612,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>561</v>
+        <v>107</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13586,13 +13624,13 @@
         <v>78</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>108</v>
@@ -13606,10 +13644,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>562</v>
+        <v>521</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>563</v>
+        <v>493</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13620,7 +13658,7 @@
         <v>79</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>78</v>
@@ -13629,16 +13667,16 @@
         <v>78</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>299</v>
+        <v>111</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>564</v>
+        <v>206</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>565</v>
+        <v>207</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13677,54 +13715,54 @@
         <v>78</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>566</v>
+        <v>118</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>567</v>
+        <v>78</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>305</v>
+        <v>78</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>568</v>
+        <v>522</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>568</v>
+        <v>495</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13732,13 +13770,13 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>78</v>
@@ -13747,16 +13785,16 @@
         <v>78</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>569</v>
+        <v>137</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>570</v>
+        <v>468</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>571</v>
+        <v>469</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>572</v>
+        <v>470</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13764,7 +13802,7 @@
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>78</v>
+        <v>519</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>78</v>
@@ -13806,19 +13844,19 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>568</v>
+        <v>472</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>78</v>
@@ -13827,7 +13865,7 @@
         <v>78</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>573</v>
+        <v>204</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>78</v>
@@ -13838,10 +13876,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>574</v>
+        <v>523</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>574</v>
+        <v>497</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13864,13 +13902,13 @@
         <v>78</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>104</v>
+        <v>329</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>105</v>
+        <v>475</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>106</v>
+        <v>476</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13921,7 +13959,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>107</v>
+        <v>479</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -13933,7 +13971,7 @@
         <v>78</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>78</v>
@@ -13942,7 +13980,7 @@
         <v>78</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
@@ -13953,21 +13991,21 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>575</v>
+        <v>524</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>575</v>
+        <v>467</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>78</v>
@@ -13979,16 +14017,16 @@
         <v>78</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>112</v>
+        <v>468</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>113</v>
+        <v>469</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>114</v>
+        <v>470</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13996,7 +14034,7 @@
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>78</v>
+        <v>525</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>78</v>
@@ -14038,19 +14076,19 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>118</v>
+        <v>472</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>78</v>
@@ -14059,7 +14097,7 @@
         <v>78</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>78</v>
@@ -14070,46 +14108,42 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>576</v>
+        <v>526</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>576</v>
+        <v>474</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>577</v>
+        <v>78</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>111</v>
+        <v>527</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>578</v>
+        <v>475</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>78</v>
       </c>
@@ -14157,19 +14191,19 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>580</v>
+        <v>479</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>78</v>
@@ -14189,10 +14223,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>581</v>
+        <v>528</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>581</v>
+        <v>529</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14200,10 +14234,10 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>78</v>
@@ -14212,16 +14246,16 @@
         <v>78</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K103" t="s" s="2">
         <v>181</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>582</v>
+        <v>530</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>583</v>
+        <v>531</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14233,7 +14267,7 @@
         <v>78</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>78</v>
+        <v>532</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>78</v>
@@ -14251,10 +14285,10 @@
         <v>259</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>584</v>
+        <v>533</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>585</v>
+        <v>534</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>78</v>
@@ -14272,42 +14306,42 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>581</v>
+        <v>535</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>78</v>
+        <v>536</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>78</v>
+        <v>537</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>78</v>
+        <v>538</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>573</v>
+        <v>539</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>78</v>
+        <v>540</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
-        <v>586</v>
+        <v>541</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>586</v>
+        <v>542</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14315,31 +14349,35 @@
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G104" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>317</v>
+        <v>104</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>587</v>
+        <v>543</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
+        <v>544</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>546</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>78</v>
       </c>
@@ -14387,7 +14425,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>586</v>
+        <v>547</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14402,16 +14440,16 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>78</v>
+        <v>548</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>78</v>
+        <v>549</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>573</v>
+        <v>550</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>78</v>
+        <v>296</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>78</v>
@@ -14419,10 +14457,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>589</v>
+        <v>551</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>589</v>
+        <v>552</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14439,24 +14477,26 @@
         <v>78</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>590</v>
+        <v>181</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>591</v>
+        <v>553</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>592</v>
+        <v>554</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="O105" s="2"/>
+        <v>555</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>556</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>78</v>
       </c>
@@ -14480,13 +14520,13 @@
         <v>78</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>78</v>
+        <v>259</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>78</v>
+        <v>557</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>78</v>
+        <v>558</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>78</v>
@@ -14504,7 +14544,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>589</v>
+        <v>559</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14519,16 +14559,16 @@
         <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>78</v>
+        <v>560</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>78</v>
+        <v>561</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>78</v>
+        <v>563</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>78</v>
@@ -14536,10 +14576,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>594</v>
+        <v>564</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>594</v>
+        <v>565</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14559,19 +14599,19 @@
         <v>78</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>590</v>
+        <v>566</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>595</v>
+        <v>567</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>596</v>
+        <v>568</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>593</v>
+        <v>569</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14621,7 +14661,7 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>594</v>
+        <v>570</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14639,10 +14679,10 @@
         <v>78</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>573</v>
+        <v>108</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>78</v>
@@ -14651,12 +14691,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>597</v>
+        <v>571</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>597</v>
+        <v>572</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14667,25 +14707,25 @@
         <v>79</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J107" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J107" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K107" t="s" s="2">
-        <v>569</v>
+        <v>299</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>598</v>
+        <v>573</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>599</v>
+        <v>574</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14736,13 +14776,13 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>597</v>
+        <v>575</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>78</v>
@@ -14754,24 +14794,24 @@
         <v>78</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>78</v>
+        <v>204</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>78</v>
+        <v>305</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="108" hidden="true">
+    <row r="108">
       <c r="A108" t="s" s="2">
-        <v>600</v>
+        <v>577</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>600</v>
+        <v>577</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14782,10 +14822,10 @@
         <v>79</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>78</v>
@@ -14794,15 +14834,17 @@
         <v>78</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>104</v>
+        <v>578</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>105</v>
+        <v>579</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N108" s="2"/>
+        <v>580</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>581</v>
+      </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>78</v>
@@ -14851,19 +14893,19 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>107</v>
+        <v>577</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>78</v>
@@ -14872,7 +14914,7 @@
         <v>78</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>108</v>
+        <v>582</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>78</v>
@@ -14883,21 +14925,21 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>601</v>
+        <v>583</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>601</v>
+        <v>583</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>78</v>
@@ -14909,17 +14951,15 @@
         <v>78</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>78</v>
@@ -14968,19 +15008,19 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>78</v>
@@ -15000,14 +15040,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>602</v>
+        <v>584</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>602</v>
+        <v>584</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>577</v>
+        <v>110</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15020,26 +15060,24 @@
         <v>78</v>
       </c>
       <c r="I110" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K110" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>578</v>
+        <v>112</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>579</v>
+        <v>113</v>
       </c>
       <c r="N110" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="O110" t="s" s="2">
-        <v>233</v>
-      </c>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>78</v>
       </c>
@@ -15087,7 +15125,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>580</v>
+        <v>118</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15108,7 +15146,7 @@
         <v>78</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>204</v>
+        <v>108</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>78</v>
@@ -15119,42 +15157,46 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>603</v>
+        <v>585</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>603</v>
+        <v>585</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>78</v>
+        <v>586</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>604</v>
+        <v>587</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="N111" s="2"/>
-      <c r="O111" s="2"/>
+        <v>588</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P111" t="s" s="2">
         <v>78</v>
       </c>
@@ -15202,19 +15244,19 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>603</v>
+        <v>589</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>78</v>
@@ -15223,7 +15265,7 @@
         <v>78</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>78</v>
@@ -15234,10 +15276,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>606</v>
+        <v>590</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>606</v>
+        <v>590</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15248,7 +15290,7 @@
         <v>79</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>78</v>
@@ -15260,13 +15302,13 @@
         <v>78</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>299</v>
+        <v>181</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>607</v>
+        <v>591</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>608</v>
+        <v>592</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15293,13 +15335,13 @@
         <v>78</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>78</v>
+        <v>259</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>78</v>
+        <v>593</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>78</v>
+        <v>594</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>78</v>
@@ -15317,13 +15359,13 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>606</v>
+        <v>590</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>78</v>
@@ -15338,7 +15380,7 @@
         <v>78</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>573</v>
+        <v>582</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>78</v>
@@ -15347,12 +15389,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>609</v>
+        <v>595</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>609</v>
+        <v>595</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15363,10 +15405,10 @@
         <v>79</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>78</v>
@@ -15375,13 +15417,13 @@
         <v>78</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>104</v>
+        <v>329</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>610</v>
+        <v>596</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>611</v>
+        <v>597</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -15432,7 +15474,7 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>609</v>
+        <v>595</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15453,7 +15495,7 @@
         <v>78</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>573</v>
+        <v>582</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>78</v>
@@ -15462,12 +15504,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>612</v>
+        <v>598</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>612</v>
+        <v>598</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15478,10 +15520,10 @@
         <v>79</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>78</v>
@@ -15490,18 +15532,18 @@
         <v>78</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>613</v>
+        <v>599</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>614</v>
+        <v>600</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="N114" s="2"/>
-      <c r="O114" t="s" s="2">
-        <v>616</v>
-      </c>
+        <v>601</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>78</v>
       </c>
@@ -15549,13 +15591,13 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>612</v>
+        <v>598</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>78</v>
@@ -15570,17 +15612,1062 @@
         <v>78</v>
       </c>
       <c r="AM114" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="O115" s="2"/>
+      <c r="P115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="N116" s="2"/>
+      <c r="O116" s="2"/>
+      <c r="P116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO116" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N117" s="2"/>
+      <c r="O117" s="2"/>
+      <c r="P117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM117" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="AN114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO114" t="s" s="2">
+      <c r="AN117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO117" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="118" hidden="true">
+      <c r="A118" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O118" s="2"/>
+      <c r="P118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO118" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="119" hidden="true">
+      <c r="A119" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="P119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO119" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="120" hidden="true">
+      <c r="A120" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="N120" s="2"/>
+      <c r="O120" s="2"/>
+      <c r="P120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO120" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="121" hidden="true">
+      <c r="A121" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="N121" s="2"/>
+      <c r="O121" s="2"/>
+      <c r="P121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO121" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="N122" s="2"/>
+      <c r="O122" s="2"/>
+      <c r="P122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO122" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="N123" s="2"/>
+      <c r="O123" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="P123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO123" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO114">
+  <autoFilter ref="A1:AO123">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15590,7 +16677,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI113">
+  <conditionalFormatting sqref="A2:AI122">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$114</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4566" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4231" uniqueCount="617">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-2</t>
+    <t>1.2.0-snapshot-1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:20:56+00:00</t>
+    <t>2026-06-16T14:13:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|1.2.0-snapshot-2</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|1.2.0-snapshot-1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -394,7 +394,7 @@
     <t>as-ext-data-trace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-1}
 </t>
   </si>
   <si>
@@ -496,7 +496,7 @@
     <t>fr-canonical</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner-role|2.2.0</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner-role|2.1.0</t>
   </si>
   <si>
     <t>PractitionerRole.meta.profile:as-dr-canonical</t>
@@ -505,7 +505,7 @@
     <t>as-dr-canonical</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dr-practitionerrole|1.2.0-snapshot-2</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dr-practitionerrole|1.2.0-snapshot-1</t>
   </si>
   <si>
     <t>PractitionerRole.meta.security</t>
@@ -673,16 +673,14 @@
     <t>serviceTypeDuration</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-service-type-duration|2.2.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-service-type-duration|2.1.0}
 </t>
   </si>
   <si>
     <t>FR Core Service Type Duration Extension</t>
   </si>
   <si>
-    <t>Cette extension française permet d'associer le type de service avec la durée de ce service.
--This French extension allows to associate the type of service with the duration of this service</t>
+    <t>This French extension allows to associate the type of service with the duration of this service | Cette extension française permet d'associer le type de service avec la durée de ce service.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -695,7 +693,7 @@
     <t>as-ext-practitionerrole-contracted</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-contracted|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-contracted|1.2.0-snapshot-1}
 </t>
   </si>
   <si>
@@ -711,7 +709,7 @@
     <t>as-ext-practitionerrole-hascas</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-hascas|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-hascas|1.2.0-snapshot-1}
 </t>
   </si>
   <si>
@@ -727,7 +725,7 @@
     <t>as-ext-practitionerrole-vitale-accepted</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-vitale-accepted|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-vitale-accepted|1.2.0-snapshot-1}
 </t>
   </si>
   <si>
@@ -788,28 +786,28 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:numeroAm</t>
-  </si>
-  <si>
-    <t>numeroAm</t>
-  </si>
-  <si>
-    <t>Identifiant d’activité propre à l’Assurance Maladie. format: 9 digits. synonyme: numeroAM</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier:numeroAm.id</t>
+    <t>PractitionerRole.identifier:idSituationExercice</t>
+  </si>
+  <si>
+    <t>idSituationExercice</t>
+  </si>
+  <si>
+    <t>Identifiant d'activité propre au RPPS</t>
+  </si>
+  <si>
+    <t>PractitionerRole.identifier:idSituationExercice.id</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.id</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:numeroAm.extension</t>
+    <t>PractitionerRole.identifier:idSituationExercice.extension</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.extension</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:numeroAm.use</t>
+    <t>PractitionerRole.identifier:idSituationExercice.use</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.use</t>
@@ -842,7 +840,7 @@
     <t>Role.code or implied by context</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:numeroAm.type</t>
+    <t>PractitionerRole.identifier:idSituationExercice.type</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.type</t>
@@ -876,7 +874,7 @@
     <t>CX.5</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:numeroAm.system</t>
+    <t>PractitionerRole.identifier:idSituationExercice.system</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.system</t>
@@ -894,7 +892,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>https://www.ameli.fr</t>
+    <t>https://rpps.esante.gouv.fr</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -912,7 +910,7 @@
     <t>./IdentifierType</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:numeroAm.value</t>
+    <t>PractitionerRole.identifier:idSituationExercice.value</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.value</t>
@@ -942,7 +940,7 @@
     <t>./Value</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:numeroAm.period</t>
+    <t>PractitionerRole.identifier:idSituationExercice.period</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.period</t>
@@ -970,7 +968,7 @@
     <t>./StartDate and ./EndDate</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:numeroAm.assigner</t>
+    <t>PractitionerRole.identifier:idSituationExercice.assigner</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.assigner</t>
@@ -1001,42 +999,6 @@
     <t>./IdentifierIssuingAuthority</t>
   </si>
   <si>
-    <t>PractitionerRole.identifier:idSituationExercice</t>
-  </si>
-  <si>
-    <t>idSituationExercice</t>
-  </si>
-  <si>
-    <t>Identifiant d'activité propre au RPPS</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier:idSituationExercice.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier:idSituationExercice.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier:idSituationExercice.use</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier:idSituationExercice.type</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier:idSituationExercice.system</t>
-  </si>
-  <si>
-    <t>https://rpps.esante.gouv.fr</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier:idSituationExercice.value</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier:idSituationExercice.period</t>
-  </si>
-  <si>
-    <t>PractitionerRole.identifier:idSituationExercice.assigner</t>
-  </si>
-  <si>
     <t>PractitionerRole.active</t>
   </si>
   <si>
@@ -1161,7 +1123,7 @@
     <t>PractitionerRole.practitioner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-2)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-1)
 </t>
   </si>
   <si>
@@ -1177,7 +1139,7 @@
     <t>PractitionerRole.organization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-2)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-1)
 </t>
   </si>
   <si>
@@ -1205,7 +1167,7 @@
     <t>Need to know what authority the practitioner has - what can they do?</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-role-exercice|2.2.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-role-exercice|2.1.0</t>
   </si>
   <si>
     <t>PRD-1 / STF-18  / PRA-3  / PRT-4  / ROL-3 / ORC-12 / OBR-16 / PV1-7 / PV1-8 / PV1-9 / PV1-17</t>
@@ -1328,7 +1290,7 @@
     <t>Specific specialty of the practitioner.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty|2.2.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty|2.1.0</t>
   </si>
   <si>
     <t>PRA-5</t>
@@ -1343,7 +1305,7 @@
     <t>PractitionerRole.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.1.0)
 </t>
   </si>
   <si>
@@ -1365,7 +1327,7 @@
     <t>PractitionerRole.healthcareService</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-healthcare-service|2.2.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-healthcare-service|2.1.0)
 </t>
   </si>
   <si>
@@ -1384,14 +1346,14 @@
     <t>PractitionerRole.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.1.0}
 </t>
   </si>
   <si>
     <t>Details of a Technology mediated contact point | Coordonnées électroniques détaillées</t>
   </si>
   <si>
-    <t>Contact details that are specific to the role/location/service.</t>
+    <t>Details for all kinds of technology mediated contact points for a person or organization, including telephone, email, etc.</t>
   </si>
   <si>
     <t>Often practitioners have a dedicated line for each location (or service) that they work at, and need to be able to define separate contact details for each of these.</t>
@@ -1401,10 +1363,20 @@
 exists:extension('https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type')}</t>
   </si>
   <si>
+    <t>cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+  </si>
+  <si>
     <t>SituationExercice.telecommunication</t>
   </si>
   <si>
-    <t>.telecom</t>
+    <t>XTN</t>
+  </si>
+  <si>
+    <t>TEL</t>
+  </si>
+  <si>
+    <t>ContactPoint</t>
   </si>
   <si>
     <t>PractitionerRole.telecom:mailbox-mss</t>
@@ -1413,7 +1385,7 @@
     <t>mailbox-mss</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-2}
+    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-1}
 </t>
   </si>
   <si>
@@ -1441,16 +1413,14 @@
     <t>emailType</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type|2.2.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type|2.1.0}
 </t>
   </si>
   <si>
     <t>Type of email | type de messagerie électronique</t>
   </si>
   <si>
-    <t>Extension permettant d'indiquer le type d'adresse email d'un ContactPoint.
-- This extension allows to specify the type of mail used to contact the person.</t>
+    <t>Extension on the ContactPoint datatype. This extension allows to specify the type of mail used to contact the person (MSSsanté|Apicrypt|OSM|Autre).</t>
   </si>
   <si>
     <t>PractitionerRole.telecom:mailbox-mss.extension:emailType.id</t>
@@ -1504,7 +1474,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-email-type|2.2.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-email-type|2.1.0</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -1516,7 +1486,7 @@
     <t>as-mailbox-mss-metadata</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-1}
 </t>
   </si>
   <si>
@@ -2274,7 +2244,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO123"/>
+  <dimension ref="A1:AO114"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="86.015625" customWidth="true" bestFit="true"/>
@@ -6422,16 +6392,14 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>316</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>78</v>
       </c>
@@ -6443,7 +6411,7 @@
         <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>78</v>
@@ -6452,22 +6420,26 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>236</v>
+        <v>317</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>318</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="O36" t="s" s="2">
-        <v>239</v>
+        <v>321</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q36" s="2"/>
+      <c r="Q36" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="R36" t="s" s="2">
         <v>78</v>
       </c>
@@ -6511,13 +6483,13 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>235</v>
+        <v>316</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>78</v>
@@ -6529,24 +6501,24 @@
         <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>242</v>
+        <v>323</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>243</v>
+        <v>324</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>245</v>
+        <v>325</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>250</v>
+        <v>326</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6560,25 +6532,27 @@
         <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>104</v>
+        <v>299</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>105</v>
+        <v>327</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>106</v>
+        <v>328</v>
       </c>
       <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+      <c r="O37" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
       </c>
@@ -6626,7 +6600,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>107</v>
+        <v>326</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6638,41 +6612,41 @@
         <v>78</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>78</v>
+        <v>330</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>108</v>
+        <v>331</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>78</v>
+        <v>332</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>78</v>
+        <v>333</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>252</v>
+        <v>334</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>78</v>
@@ -6684,17 +6658,15 @@
         <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -6731,31 +6703,31 @@
         <v>78</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>78</v>
@@ -6775,46 +6747,44 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>254</v>
+        <v>335</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>181</v>
+        <v>111</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>255</v>
+        <v>112</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>256</v>
+        <v>113</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>78</v>
       </c>
@@ -6838,52 +6808,52 @@
         <v>78</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>259</v>
+        <v>78</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>260</v>
+        <v>78</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>261</v>
+        <v>78</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>262</v>
+        <v>118</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>263</v>
+        <v>108</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>
@@ -6894,10 +6864,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>265</v>
+        <v>336</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6920,20 +6890,18 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>266</v>
+        <v>337</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>267</v>
+        <v>338</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>268</v>
+        <v>339</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>78</v>
       </c>
@@ -6957,13 +6925,13 @@
         <v>78</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>163</v>
+        <v>78</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>271</v>
+        <v>78</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>272</v>
+        <v>78</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>78</v>
@@ -6981,7 +6949,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>273</v>
+        <v>341</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6990,19 +6958,19 @@
         <v>90</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>78</v>
+        <v>343</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>274</v>
+        <v>344</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>263</v>
+        <v>345</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
@@ -7013,10 +6981,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>323</v>
+        <v>346</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>276</v>
+        <v>346</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7024,7 +6992,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>90</v>
@@ -7039,32 +7007,32 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>137</v>
+        <v>337</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>277</v>
+        <v>347</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>278</v>
+        <v>348</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q41" s="2"/>
+      <c r="Q41" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="R41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>324</v>
+        <v>78</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>282</v>
+        <v>78</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>78</v>
@@ -7100,7 +7068,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>283</v>
+        <v>351</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7109,33 +7077,33 @@
         <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>78</v>
+        <v>352</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>284</v>
+        <v>353</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>285</v>
+        <v>354</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>286</v>
+        <v>78</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>288</v>
+        <v>355</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7143,13 +7111,13 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>78</v>
@@ -7158,17 +7126,15 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>104</v>
+        <v>356</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>289</v>
+        <v>357</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -7181,7 +7147,7 @@
         <v>78</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>292</v>
+        <v>78</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>78</v>
@@ -7217,7 +7183,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>293</v>
+        <v>355</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7235,24 +7201,24 @@
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>294</v>
+        <v>78</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>295</v>
+        <v>359</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>296</v>
+        <v>78</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>326</v>
+        <v>360</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>298</v>
+        <v>360</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7266,7 +7232,7 @@
         <v>90</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>78</v>
@@ -7275,13 +7241,13 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>299</v>
+        <v>361</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>300</v>
+        <v>362</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>301</v>
+        <v>363</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7332,7 +7298,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>302</v>
+        <v>360</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7350,13 +7316,13 @@
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>303</v>
+        <v>78</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>305</v>
+        <v>78</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>78</v>
@@ -7364,10 +7330,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>327</v>
+        <v>365</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>307</v>
+        <v>365</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7378,7 +7344,7 @@
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>78</v>
@@ -7390,18 +7356,20 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>308</v>
+        <v>266</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>309</v>
+        <v>366</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>310</v>
+        <v>367</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>369</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
       </c>
@@ -7425,37 +7393,33 @@
         <v>78</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>78</v>
+        <v>370</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>312</v>
+        <v>365</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>78</v>
@@ -7467,13 +7431,13 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>313</v>
+        <v>371</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>314</v>
+        <v>372</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>78</v>
@@ -7481,12 +7445,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>328</v>
+        <v>373</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="C45" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="D45" t="s" s="2">
         <v>78</v>
       </c>
@@ -7507,26 +7473,24 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>329</v>
+        <v>266</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>331</v>
+        <v>367</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>332</v>
+        <v>368</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>333</v>
+        <v>369</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q45" t="s" s="2">
-        <v>334</v>
-      </c>
+      <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
         <v>78</v>
       </c>
@@ -7546,13 +7510,11 @@
         <v>78</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>78</v>
+        <v>376</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>78</v>
@@ -7570,13 +7532,13 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>328</v>
+        <v>365</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>78</v>
@@ -7585,29 +7547,31 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>78</v>
+        <v>377</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>335</v>
+        <v>371</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>336</v>
+        <v>372</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>78</v>
+        <v>332</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>337</v>
+        <v>78</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>338</v>
+        <v>378</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="C46" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="D46" t="s" s="2">
         <v>78</v>
       </c>
@@ -7628,17 +7592,19 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>299</v>
+        <v>266</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>339</v>
+        <v>380</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="O46" t="s" s="2">
-        <v>341</v>
+        <v>369</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
@@ -7663,13 +7629,11 @@
         <v>78</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>78</v>
+        <v>381</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>78</v>
@@ -7687,13 +7651,13 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>338</v>
+        <v>365</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>78</v>
@@ -7702,29 +7666,31 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>78</v>
+        <v>382</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>342</v>
+        <v>371</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>343</v>
+        <v>372</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>345</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>346</v>
+        <v>383</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="C47" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="D47" t="s" s="2">
         <v>78</v>
       </c>
@@ -7736,25 +7702,29 @@
         <v>90</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>104</v>
+        <v>266</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>105</v>
+        <v>385</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>369</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>78</v>
       </c>
@@ -7778,13 +7748,11 @@
         <v>78</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>78</v>
+        <v>386</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>78</v>
@@ -7802,76 +7770,80 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>107</v>
+        <v>365</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>78</v>
+        <v>387</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>78</v>
+        <v>371</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>108</v>
+        <v>372</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>78</v>
+        <v>332</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>347</v>
+        <v>388</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="D48" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>111</v>
+        <v>266</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>112</v>
+        <v>390</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>113</v>
+        <v>367</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>369</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
       </c>
@@ -7895,31 +7867,29 @@
         <v>78</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>78</v>
+        <v>391</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>118</v>
+        <v>365</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7931,32 +7901,34 @@
         <v>78</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>78</v>
+        <v>392</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>78</v>
+        <v>371</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>108</v>
+        <v>372</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>78</v>
+        <v>332</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>348</v>
+        <v>393</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>394</v>
+      </c>
       <c r="D49" t="s" s="2">
         <v>78</v>
       </c>
@@ -7968,7 +7940,7 @@
         <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>78</v>
@@ -7977,18 +7949,20 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>349</v>
+        <v>266</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>350</v>
+        <v>395</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>351</v>
+        <v>367</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>369</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
       </c>
@@ -8012,13 +7986,11 @@
         <v>78</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>78</v>
+        <v>396</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>78</v>
@@ -8036,44 +8008,46 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>354</v>
+        <v>78</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>355</v>
+        <v>397</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>78</v>
+        <v>332</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>358</v>
+        <v>398</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="D50" t="s" s="2">
         <v>78</v>
       </c>
@@ -8085,7 +8059,7 @@
         <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>78</v>
@@ -8094,24 +8068,24 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>349</v>
+        <v>266</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>359</v>
+        <v>400</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>369</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q50" t="s" s="2">
-        <v>362</v>
-      </c>
+      <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
         <v>78</v>
       </c>
@@ -8131,13 +8105,11 @@
         <v>78</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>78</v>
+        <v>401</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>78</v>
@@ -8155,31 +8127,31 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>354</v>
+        <v>78</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>364</v>
+        <v>402</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>78</v>
+        <v>332</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>78</v>
@@ -8187,21 +8159,23 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>367</v>
+        <v>403</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C51" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="D51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>91</v>
@@ -8213,16 +8187,20 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="M51" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>78</v>
       </c>
@@ -8246,13 +8224,11 @@
         <v>78</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>78</v>
+        <v>406</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>78</v>
@@ -8270,13 +8246,13 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>78</v>
@@ -8285,27 +8261,27 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>78</v>
+        <v>407</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>78</v>
+        <v>371</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>78</v>
+        <v>332</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>372</v>
+        <v>408</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>372</v>
+        <v>408</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8316,10 +8292,10 @@
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>78</v>
@@ -8328,13 +8304,13 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>373</v>
+        <v>266</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>374</v>
+        <v>409</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8361,13 +8337,11 @@
         <v>78</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>78</v>
+        <v>411</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>78</v>
@@ -8385,13 +8359,13 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>372</v>
+        <v>408</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>78</v>
@@ -8403,13 +8377,13 @@
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>78</v>
+        <v>412</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>376</v>
+        <v>413</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>78</v>
+        <v>414</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>78</v>
@@ -8417,10 +8391,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>377</v>
+        <v>415</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>377</v>
+        <v>415</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8443,20 +8417,16 @@
         <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>266</v>
+        <v>416</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>378</v>
+        <v>417</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>381</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>78</v>
       </c>
@@ -8480,27 +8450,31 @@
         <v>78</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y53" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z53" t="s" s="2">
-        <v>382</v>
+        <v>78</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="AC53" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>377</v>
+        <v>415</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8518,28 +8492,26 @@
         <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>383</v>
+        <v>78</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>384</v>
+        <v>419</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>344</v>
+        <v>420</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>78</v>
+        <v>421</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>385</v>
+        <v>422</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>386</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>78</v>
       </c>
@@ -8548,7 +8520,7 @@
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>91</v>
@@ -8557,23 +8529,19 @@
         <v>78</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>266</v>
+        <v>423</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>387</v>
+        <v>424</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>381</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>78</v>
       </c>
@@ -8597,11 +8565,13 @@
         <v>78</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="Y54" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z54" t="s" s="2">
-        <v>388</v>
+        <v>78</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8619,7 +8589,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>377</v>
+        <v>422</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8634,31 +8604,29 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>383</v>
+        <v>426</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>384</v>
+        <v>427</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>344</v>
+        <v>78</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>78</v>
       </c>
@@ -8667,7 +8635,7 @@
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>91</v>
@@ -8676,22 +8644,20 @@
         <v>78</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>266</v>
+        <v>429</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>392</v>
+        <v>430</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>380</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>381</v>
+        <v>432</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8716,29 +8682,29 @@
         <v>78</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="Y55" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z55" t="s" s="2">
-        <v>393</v>
+        <v>78</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>377</v>
+        <v>428</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8747,36 +8713,36 @@
         <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>78</v>
+        <v>214</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>102</v>
+        <v>434</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>394</v>
+        <v>435</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>383</v>
+        <v>436</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>384</v>
+        <v>437</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>344</v>
+        <v>438</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>395</v>
+        <v>439</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>377</v>
+        <v>428</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>396</v>
+        <v>440</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>78</v>
@@ -8786,31 +8752,29 @@
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>266</v>
+        <v>441</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>397</v>
+        <v>442</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>380</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>381</v>
+        <v>432</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8835,11 +8799,13 @@
         <v>78</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="Y56" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z56" t="s" s="2">
-        <v>398</v>
+        <v>78</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>78</v>
@@ -8857,7 +8823,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>377</v>
+        <v>428</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8866,37 +8832,35 @@
         <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>78</v>
+        <v>214</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>102</v>
+        <v>434</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>399</v>
+        <v>443</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>383</v>
+        <v>436</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>384</v>
+        <v>437</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>344</v>
+        <v>438</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>400</v>
+        <v>444</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>78</v>
       </c>
@@ -8908,29 +8872,25 @@
         <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>266</v>
+        <v>104</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>402</v>
+        <v>105</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>381</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>78</v>
       </c>
@@ -8954,11 +8914,13 @@
         <v>78</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="Y57" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z57" t="s" s="2">
-        <v>403</v>
+        <v>78</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>78</v>
@@ -8976,80 +8938,74 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>377</v>
+        <v>107</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>404</v>
+        <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>383</v>
+        <v>78</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>384</v>
+        <v>108</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>344</v>
+        <v>78</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>405</v>
+        <v>446</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>406</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>266</v>
+        <v>111</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>407</v>
+        <v>206</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>381</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>78</v>
       </c>
@@ -9073,29 +9029,31 @@
         <v>78</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="Y58" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z58" t="s" s="2">
-        <v>408</v>
+        <v>78</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>377</v>
+        <v>118</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9107,68 +9065,64 @@
         <v>78</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>409</v>
+        <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>383</v>
+        <v>78</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>384</v>
+        <v>78</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>344</v>
+        <v>78</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>410</v>
+        <v>448</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>377</v>
+        <v>447</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>411</v>
+        <v>449</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>266</v>
+        <v>450</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>412</v>
+        <v>451</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>381</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>78</v>
       </c>
@@ -9192,11 +9146,13 @@
         <v>78</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="Y59" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z59" t="s" s="2">
-        <v>413</v>
+        <v>78</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>78</v>
@@ -9214,7 +9170,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>377</v>
+        <v>118</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9226,34 +9182,32 @@
         <v>78</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>414</v>
+        <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>383</v>
+        <v>78</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>384</v>
+        <v>78</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>344</v>
+        <v>78</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>415</v>
+        <v>453</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="C60" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>78</v>
       </c>
@@ -9262,32 +9216,28 @@
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>266</v>
+        <v>104</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>417</v>
+        <v>105</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>381</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>78</v>
       </c>
@@ -9311,11 +9261,13 @@
         <v>78</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="Y60" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z60" t="s" s="2">
-        <v>418</v>
+        <v>78</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
@@ -9333,31 +9285,31 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>377</v>
+        <v>107</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>419</v>
+        <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>383</v>
+        <v>78</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>384</v>
+        <v>108</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>344</v>
+        <v>78</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>78</v>
@@ -9365,10 +9317,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>420</v>
+        <v>455</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>420</v>
+        <v>456</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9388,16 +9340,16 @@
         <v>78</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>266</v>
+        <v>111</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>421</v>
+        <v>206</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>422</v>
+        <v>207</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9424,29 +9376,31 @@
         <v>78</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="Y61" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z61" t="s" s="2">
-        <v>423</v>
+        <v>78</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>420</v>
+        <v>118</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9458,19 +9412,19 @@
         <v>78</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>424</v>
+        <v>78</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>425</v>
+        <v>78</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>426</v>
+        <v>78</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>78</v>
@@ -9478,10 +9432,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>427</v>
+        <v>457</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>427</v>
+        <v>458</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9489,10 +9443,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>78</v>
@@ -9501,25 +9455,27 @@
         <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>428</v>
+        <v>137</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>429</v>
+        <v>459</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>460</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>78</v>
+        <v>462</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>78</v>
@@ -9561,19 +9517,19 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>427</v>
+        <v>463</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>78</v>
@@ -9582,21 +9538,21 @@
         <v>78</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>431</v>
+        <v>204</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>432</v>
+        <v>78</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>433</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>434</v>
+        <v>464</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>434</v>
+        <v>465</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9607,10 +9563,10 @@
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>78</v>
@@ -9619,13 +9575,13 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>435</v>
+        <v>159</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>436</v>
+        <v>466</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>437</v>
+        <v>467</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9637,7 +9593,7 @@
         <v>78</v>
       </c>
       <c r="S63" t="s" s="2">
-        <v>78</v>
+        <v>468</v>
       </c>
       <c r="T63" t="s" s="2">
         <v>78</v>
@@ -9652,13 +9608,11 @@
         <v>78</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>78</v>
+        <v>469</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>78</v>
@@ -9676,13 +9630,13 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>434</v>
+        <v>470</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>78</v>
@@ -9694,10 +9648,10 @@
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>438</v>
+        <v>78</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>439</v>
+        <v>204</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -9708,12 +9662,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>440</v>
+        <v>471</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C64" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>472</v>
+      </c>
       <c r="D64" t="s" s="2">
         <v>78</v>
       </c>
@@ -9722,30 +9678,28 @@
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>441</v>
+        <v>473</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>442</v>
+        <v>474</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>443</v>
+        <v>475</v>
       </c>
       <c r="N64" s="2"/>
-      <c r="O64" t="s" s="2">
-        <v>444</v>
-      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>78</v>
       </c>
@@ -9781,17 +9735,19 @@
         <v>78</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AC64" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>440</v>
+        <v>118</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9803,16 +9759,16 @@
         <v>78</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>446</v>
+        <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>447</v>
+        <v>78</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -9823,14 +9779,12 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>448</v>
+        <v>476</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>78</v>
       </c>
@@ -9839,7 +9793,7 @@
         <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>78</v>
@@ -9848,21 +9802,19 @@
         <v>78</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>450</v>
+        <v>104</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>451</v>
+        <v>105</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>443</v>
+        <v>106</v>
       </c>
       <c r="N65" s="2"/>
-      <c r="O65" t="s" s="2">
-        <v>444</v>
-      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>78</v>
       </c>
@@ -9910,28 +9862,28 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>440</v>
+        <v>107</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>452</v>
+        <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>447</v>
+        <v>108</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
@@ -9942,21 +9894,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>453</v>
+        <v>477</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>78</v>
@@ -9968,15 +9920,17 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -10013,31 +9967,31 @@
         <v>78</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
@@ -10057,21 +10011,23 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>455</v>
+        <v>478</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="C67" s="2"/>
+      <c r="C67" t="s" s="2">
+        <v>479</v>
+      </c>
       <c r="D67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>78</v>
@@ -10086,7 +10042,7 @@
         <v>111</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>206</v>
+        <v>480</v>
       </c>
       <c r="M67" t="s" s="2">
         <v>207</v>
@@ -10128,16 +10084,16 @@
         <v>78</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>118</v>
@@ -10172,20 +10128,18 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>457</v>
+        <v>481</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="C68" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>90</v>
@@ -10200,13 +10154,13 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>459</v>
+        <v>104</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>460</v>
+        <v>105</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>461</v>
+        <v>106</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10257,19 +10211,19 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>78</v>
@@ -10278,7 +10232,7 @@
         <v>78</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>78</v>
@@ -10289,10 +10243,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>463</v>
+        <v>484</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10303,7 +10257,7 @@
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>78</v>
@@ -10315,13 +10269,13 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>105</v>
+        <v>206</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>106</v>
+        <v>207</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10360,31 +10314,31 @@
         <v>78</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>78</v>
@@ -10393,7 +10347,7 @@
         <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>78</v>
@@ -10404,10 +10358,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10415,10 +10369,10 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>78</v>
@@ -10430,22 +10384,24 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>206</v>
+        <v>459</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>460</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>78</v>
+        <v>479</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>78</v>
@@ -10475,31 +10431,31 @@
         <v>78</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>118</v>
+        <v>463</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>78</v>
@@ -10508,7 +10464,7 @@
         <v>78</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>78</v>
+        <v>204</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>78</v>
@@ -10519,10 +10475,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>466</v>
+        <v>487</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>467</v>
+        <v>488</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10530,7 +10486,7 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>90</v>
@@ -10545,24 +10501,22 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>137</v>
+        <v>266</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>470</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>471</v>
+        <v>78</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>78</v>
@@ -10580,13 +10534,11 @@
         <v>78</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>78</v>
+        <v>489</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>78</v>
@@ -10604,10 +10556,10 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>90</v>
@@ -10616,7 +10568,7 @@
         <v>78</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>78</v>
@@ -10636,12 +10588,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>473</v>
+        <v>490</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C72" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="C72" t="s" s="2">
+        <v>491</v>
+      </c>
       <c r="D72" t="s" s="2">
         <v>78</v>
       </c>
@@ -10662,13 +10616,13 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>159</v>
+        <v>111</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>475</v>
+        <v>206</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>476</v>
+        <v>207</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10680,7 +10634,7 @@
         <v>78</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>477</v>
+        <v>78</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>78</v>
@@ -10695,11 +10649,13 @@
         <v>78</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Y72" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z72" t="s" s="2">
-        <v>478</v>
+        <v>78</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>78</v>
@@ -10717,19 +10673,19 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>479</v>
+        <v>118</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>78</v>
@@ -10738,7 +10694,7 @@
         <v>78</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -10749,14 +10705,12 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="C73" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>78</v>
       </c>
@@ -10777,13 +10731,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>482</v>
+        <v>104</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>483</v>
+        <v>105</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>484</v>
+        <v>106</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10834,19 +10788,19 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>78</v>
@@ -10855,7 +10809,7 @@
         <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10866,10 +10820,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>463</v>
+        <v>484</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10880,7 +10834,7 @@
         <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>78</v>
@@ -10892,13 +10846,13 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>105</v>
+        <v>206</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>106</v>
+        <v>207</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10937,31 +10891,31 @@
         <v>78</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>78</v>
@@ -10970,7 +10924,7 @@
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -10981,21 +10935,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="B75" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>78</v>
@@ -11007,16 +10961,16 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>112</v>
+        <v>459</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>113</v>
+        <v>460</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>114</v>
+        <v>461</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11024,7 +10978,7 @@
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>78</v>
+        <v>491</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>78</v>
@@ -11054,31 +11008,31 @@
         <v>78</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>118</v>
+        <v>463</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>78</v>
@@ -11087,7 +11041,7 @@
         <v>78</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>78</v>
@@ -11098,14 +11052,12 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C76" t="s" s="2">
         <v>488</v>
       </c>
+      <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>78</v>
       </c>
@@ -11126,13 +11078,13 @@
         <v>78</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>207</v>
+        <v>467</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11183,19 +11135,19 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>118</v>
+        <v>470</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>78</v>
@@ -11204,7 +11156,7 @@
         <v>78</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>78</v>
+        <v>204</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>78</v>
@@ -11215,12 +11167,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C77" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>497</v>
+      </c>
       <c r="D77" t="s" s="2">
         <v>78</v>
       </c>
@@ -11241,13 +11195,13 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>105</v>
+        <v>498</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>106</v>
+        <v>207</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11298,19 +11252,19 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>78</v>
@@ -11319,7 +11273,7 @@
         <v>78</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>78</v>
@@ -11330,10 +11284,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11344,7 +11298,7 @@
         <v>79</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>78</v>
@@ -11356,13 +11310,13 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>206</v>
+        <v>105</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>207</v>
+        <v>106</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11401,31 +11355,31 @@
         <v>78</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>78</v>
@@ -11434,7 +11388,7 @@
         <v>78</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -11445,10 +11399,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11456,10 +11410,10 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>78</v>
@@ -11471,24 +11425,22 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>468</v>
+        <v>206</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>470</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>488</v>
+        <v>78</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>78</v>
@@ -11518,31 +11470,31 @@
         <v>78</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>472</v>
+        <v>118</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>78</v>
@@ -11551,7 +11503,7 @@
         <v>78</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
@@ -11562,10 +11514,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11573,7 +11525,7 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>90</v>
@@ -11588,22 +11540,24 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>266</v>
+        <v>137</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>460</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
-        <v>78</v>
+        <v>497</v>
       </c>
       <c r="S80" t="s" s="2">
         <v>78</v>
@@ -11621,11 +11575,13 @@
         <v>78</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="Y80" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z80" t="s" s="2">
-        <v>498</v>
+        <v>78</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>78</v>
@@ -11643,10 +11599,10 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>90</v>
@@ -11655,7 +11611,7 @@
         <v>78</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>78</v>
@@ -11675,14 +11631,12 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C81" t="s" s="2">
-        <v>500</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
         <v>78</v>
       </c>
@@ -11703,13 +11657,13 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>206</v>
+        <v>466</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>207</v>
+        <v>467</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11760,19 +11714,19 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>118</v>
+        <v>470</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>78</v>
@@ -11781,7 +11735,7 @@
         <v>78</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>78</v>
+        <v>204</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
@@ -11792,12 +11746,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C82" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>504</v>
+      </c>
       <c r="D82" t="s" s="2">
         <v>78</v>
       </c>
@@ -11818,13 +11774,13 @@
         <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>105</v>
+        <v>206</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>106</v>
+        <v>207</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11875,19 +11831,19 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>78</v>
@@ -11896,7 +11852,7 @@
         <v>78</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>78</v>
@@ -11907,10 +11863,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11921,7 +11877,7 @@
         <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>78</v>
@@ -11933,13 +11889,13 @@
         <v>78</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>206</v>
+        <v>105</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>207</v>
+        <v>106</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11978,31 +11934,31 @@
         <v>78</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>78</v>
@@ -12011,7 +11967,7 @@
         <v>78</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>78</v>
@@ -12022,10 +11978,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12033,10 +11989,10 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>78</v>
@@ -12048,24 +12004,22 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>468</v>
+        <v>206</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>470</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
-        <v>500</v>
+        <v>78</v>
       </c>
       <c r="S84" t="s" s="2">
         <v>78</v>
@@ -12095,31 +12049,31 @@
         <v>78</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>472</v>
+        <v>118</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>78</v>
@@ -12128,7 +12082,7 @@
         <v>78</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>78</v>
@@ -12139,10 +12093,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12150,7 +12104,7 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>90</v>
@@ -12165,22 +12119,24 @@
         <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N85" s="2"/>
+        <v>460</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
-        <v>78</v>
+        <v>504</v>
       </c>
       <c r="S85" t="s" s="2">
         <v>78</v>
@@ -12222,10 +12178,10 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>90</v>
@@ -12234,7 +12190,7 @@
         <v>78</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>78</v>
@@ -12254,14 +12210,12 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>506</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>78</v>
       </c>
@@ -12282,13 +12236,13 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>507</v>
+        <v>466</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>207</v>
+        <v>467</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12339,19 +12293,19 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>118</v>
+        <v>470</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>78</v>
@@ -12360,7 +12314,7 @@
         <v>78</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>78</v>
+        <v>204</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>78</v>
@@ -12371,12 +12325,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C87" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="C87" t="s" s="2">
+        <v>510</v>
+      </c>
       <c r="D87" t="s" s="2">
         <v>78</v>
       </c>
@@ -12397,13 +12353,13 @@
         <v>78</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>105</v>
+        <v>206</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>106</v>
+        <v>207</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12454,19 +12410,19 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>78</v>
@@ -12475,7 +12431,7 @@
         <v>78</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>78</v>
@@ -12486,10 +12442,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12500,7 +12456,7 @@
         <v>79</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>78</v>
@@ -12512,13 +12468,13 @@
         <v>78</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>206</v>
+        <v>105</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>207</v>
+        <v>106</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12557,31 +12513,31 @@
         <v>78</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>78</v>
@@ -12590,7 +12546,7 @@
         <v>78</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>78</v>
@@ -12601,10 +12557,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12612,10 +12568,10 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>78</v>
@@ -12627,24 +12583,22 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>468</v>
+        <v>206</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>470</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q89" s="2"/>
       <c r="R89" t="s" s="2">
-        <v>506</v>
+        <v>78</v>
       </c>
       <c r="S89" t="s" s="2">
         <v>78</v>
@@ -12674,31 +12628,31 @@
         <v>78</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>472</v>
+        <v>118</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>78</v>
@@ -12707,7 +12661,7 @@
         <v>78</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>78</v>
@@ -12718,10 +12672,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12729,7 +12683,7 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>90</v>
@@ -12744,22 +12698,24 @@
         <v>78</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>460</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>78</v>
+        <v>510</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>78</v>
@@ -12801,10 +12757,10 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>90</v>
@@ -12813,7 +12769,7 @@
         <v>78</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>78</v>
@@ -12833,14 +12789,12 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C91" t="s" s="2">
-        <v>513</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
         <v>78</v>
       </c>
@@ -12861,13 +12815,13 @@
         <v>78</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>111</v>
+        <v>317</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>206</v>
+        <v>466</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>207</v>
+        <v>467</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12918,19 +12872,19 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>118</v>
+        <v>470</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>78</v>
@@ -12939,7 +12893,7 @@
         <v>78</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>78</v>
+        <v>204</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>78</v>
@@ -12950,10 +12904,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>491</v>
+        <v>458</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12961,7 +12915,7 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>90</v>
@@ -12976,22 +12930,24 @@
         <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>105</v>
+        <v>459</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>460</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>78</v>
+        <v>516</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>78</v>
@@ -13033,10 +12989,10 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>107</v>
+        <v>463</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>90</v>
@@ -13054,7 +13010,7 @@
         <v>78</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>78</v>
@@ -13065,10 +13021,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>493</v>
+        <v>465</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13091,13 +13047,13 @@
         <v>78</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>111</v>
+        <v>518</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>206</v>
+        <v>466</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>207</v>
+        <v>467</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13136,31 +13092,31 @@
         <v>78</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>118</v>
+        <v>470</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>78</v>
@@ -13169,7 +13125,7 @@
         <v>78</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>78</v>
+        <v>204</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>78</v>
@@ -13180,10 +13136,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>495</v>
+        <v>520</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13203,30 +13159,28 @@
         <v>78</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>468</v>
+        <v>521</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>470</v>
-      </c>
+        <v>522</v>
+      </c>
+      <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q94" s="2"/>
       <c r="R94" t="s" s="2">
-        <v>513</v>
+        <v>78</v>
       </c>
       <c r="S94" t="s" s="2">
-        <v>78</v>
+        <v>523</v>
       </c>
       <c r="T94" t="s" s="2">
         <v>78</v>
@@ -13241,13 +13195,13 @@
         <v>78</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>78</v>
+        <v>259</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>78</v>
+        <v>524</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>78</v>
+        <v>525</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>78</v>
@@ -13265,42 +13219,42 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>472</v>
+        <v>526</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>78</v>
+        <v>527</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>78</v>
+        <v>528</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>78</v>
+        <v>529</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>204</v>
+        <v>530</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>78</v>
+        <v>531</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
-        <v>517</v>
+        <v>532</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>497</v>
+        <v>533</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13308,31 +13262,35 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>475</v>
+        <v>534</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
+        <v>535</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>78</v>
       </c>
@@ -13380,7 +13338,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>479</v>
+        <v>538</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13395,16 +13353,16 @@
         <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>78</v>
+        <v>539</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>78</v>
+        <v>540</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>204</v>
+        <v>541</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>78</v>
+        <v>296</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>78</v>
@@ -13412,14 +13370,12 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C96" t="s" s="2">
-        <v>519</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
         <v>78</v>
       </c>
@@ -13434,22 +13390,26 @@
         <v>78</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>111</v>
+        <v>181</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>206</v>
+        <v>544</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
+        <v>545</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>547</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>78</v>
       </c>
@@ -13473,13 +13433,13 @@
         <v>78</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>78</v>
+        <v>259</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>78</v>
+        <v>548</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>78</v>
+        <v>549</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>78</v>
@@ -13497,31 +13457,31 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>118</v>
+        <v>550</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>78</v>
+        <v>551</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>78</v>
+        <v>552</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>78</v>
+        <v>553</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>78</v>
+        <v>554</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>78</v>
@@ -13529,10 +13489,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>520</v>
+        <v>555</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>491</v>
+        <v>556</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13552,18 +13512,20 @@
         <v>78</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>104</v>
+        <v>557</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>105</v>
+        <v>558</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N97" s="2"/>
+        <v>559</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>560</v>
+      </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>78</v>
@@ -13612,7 +13574,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>107</v>
+        <v>561</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13624,13 +13586,13 @@
         <v>78</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>108</v>
@@ -13644,10 +13606,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>521</v>
+        <v>562</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>493</v>
+        <v>563</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13658,7 +13620,7 @@
         <v>79</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>78</v>
@@ -13667,16 +13629,16 @@
         <v>78</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>111</v>
+        <v>299</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>206</v>
+        <v>564</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>207</v>
+        <v>565</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13715,54 +13677,54 @@
         <v>78</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>118</v>
+        <v>566</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>78</v>
+        <v>204</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>78</v>
+        <v>567</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>78</v>
+        <v>305</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="99" hidden="true">
+    <row r="99">
       <c r="A99" t="s" s="2">
-        <v>522</v>
+        <v>568</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>495</v>
+        <v>568</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13770,13 +13732,13 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>78</v>
@@ -13785,16 +13747,16 @@
         <v>78</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>137</v>
+        <v>569</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>468</v>
+        <v>570</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>469</v>
+        <v>571</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>470</v>
+        <v>572</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13802,7 +13764,7 @@
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>519</v>
+        <v>78</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>78</v>
@@ -13844,19 +13806,19 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>472</v>
+        <v>568</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>78</v>
@@ -13865,7 +13827,7 @@
         <v>78</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>204</v>
+        <v>573</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>78</v>
@@ -13876,10 +13838,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>523</v>
+        <v>574</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>497</v>
+        <v>574</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13902,13 +13864,13 @@
         <v>78</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>329</v>
+        <v>104</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>475</v>
+        <v>105</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>476</v>
+        <v>106</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13959,7 +13921,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>479</v>
+        <v>107</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -13971,7 +13933,7 @@
         <v>78</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>78</v>
@@ -13980,7 +13942,7 @@
         <v>78</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>204</v>
+        <v>108</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
@@ -13991,21 +13953,21 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>524</v>
+        <v>575</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>467</v>
+        <v>575</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>78</v>
@@ -14017,16 +13979,16 @@
         <v>78</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>468</v>
+        <v>112</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>469</v>
+        <v>113</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>470</v>
+        <v>114</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14034,7 +13996,7 @@
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>525</v>
+        <v>78</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>78</v>
@@ -14076,19 +14038,19 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>472</v>
+        <v>118</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>78</v>
@@ -14097,7 +14059,7 @@
         <v>78</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>204</v>
+        <v>108</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>78</v>
@@ -14108,42 +14070,46 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>526</v>
+        <v>576</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>474</v>
+        <v>576</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>78</v>
+        <v>577</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>527</v>
+        <v>111</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>475</v>
+        <v>578</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
+        <v>579</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>78</v>
       </c>
@@ -14191,19 +14157,19 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>479</v>
+        <v>580</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>78</v>
@@ -14223,10 +14189,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>528</v>
+        <v>581</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>529</v>
+        <v>581</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14234,10 +14200,10 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>78</v>
@@ -14246,16 +14212,16 @@
         <v>78</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K103" t="s" s="2">
         <v>181</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>530</v>
+        <v>582</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>531</v>
+        <v>583</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14267,7 +14233,7 @@
         <v>78</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>532</v>
+        <v>78</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>78</v>
@@ -14285,10 +14251,10 @@
         <v>259</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>533</v>
+        <v>584</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>534</v>
+        <v>585</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>78</v>
@@ -14306,42 +14272,42 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>535</v>
+        <v>581</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>536</v>
+        <v>78</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>537</v>
+        <v>78</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>538</v>
+        <v>78</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>539</v>
+        <v>573</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>540</v>
+        <v>78</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>541</v>
+        <v>586</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>542</v>
+        <v>586</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14349,35 +14315,31 @@
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G104" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>104</v>
+        <v>317</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>543</v>
+        <v>587</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>546</v>
-      </c>
+        <v>588</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>78</v>
       </c>
@@ -14425,7 +14387,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>547</v>
+        <v>586</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14440,16 +14402,16 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>548</v>
+        <v>78</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>549</v>
+        <v>78</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>550</v>
+        <v>573</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>296</v>
+        <v>78</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>78</v>
@@ -14457,10 +14419,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>551</v>
+        <v>589</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>552</v>
+        <v>589</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14477,26 +14439,24 @@
         <v>78</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>181</v>
+        <v>590</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>553</v>
+        <v>591</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>554</v>
+        <v>592</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>556</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>78</v>
       </c>
@@ -14520,13 +14480,13 @@
         <v>78</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>259</v>
+        <v>78</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>557</v>
+        <v>78</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>558</v>
+        <v>78</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>78</v>
@@ -14544,7 +14504,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>559</v>
+        <v>589</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14559,16 +14519,16 @@
         <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>560</v>
+        <v>78</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>561</v>
+        <v>78</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>563</v>
+        <v>78</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>78</v>
@@ -14576,10 +14536,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>564</v>
+        <v>594</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>565</v>
+        <v>594</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14599,19 +14559,19 @@
         <v>78</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>566</v>
+        <v>590</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>567</v>
+        <v>595</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>568</v>
+        <v>596</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>569</v>
+        <v>593</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14661,7 +14621,7 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>570</v>
+        <v>594</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14679,10 +14639,10 @@
         <v>78</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>108</v>
+        <v>573</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>78</v>
@@ -14691,12 +14651,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="107" hidden="true">
+    <row r="107">
       <c r="A107" t="s" s="2">
-        <v>571</v>
+        <v>597</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>572</v>
+        <v>597</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14707,25 +14667,25 @@
         <v>79</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>299</v>
+        <v>569</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>573</v>
+        <v>598</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>574</v>
+        <v>599</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14776,13 +14736,13 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>575</v>
+        <v>597</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>78</v>
@@ -14794,24 +14754,24 @@
         <v>78</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>305</v>
+        <v>78</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>577</v>
+        <v>600</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>577</v>
+        <v>600</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14822,10 +14782,10 @@
         <v>79</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>78</v>
@@ -14834,17 +14794,15 @@
         <v>78</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>578</v>
+        <v>104</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>579</v>
+        <v>105</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>581</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>78</v>
@@ -14893,19 +14851,19 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>577</v>
+        <v>107</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>78</v>
@@ -14914,7 +14872,7 @@
         <v>78</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>582</v>
+        <v>108</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>78</v>
@@ -14925,21 +14883,21 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>583</v>
+        <v>601</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>583</v>
+        <v>601</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>78</v>
@@ -14951,15 +14909,17 @@
         <v>78</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N109" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>78</v>
@@ -15008,19 +14968,19 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>78</v>
@@ -15040,14 +15000,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>584</v>
+        <v>602</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>584</v>
+        <v>602</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>110</v>
+        <v>577</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15060,24 +15020,26 @@
         <v>78</v>
       </c>
       <c r="I110" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K110" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>112</v>
+        <v>578</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>113</v>
+        <v>579</v>
       </c>
       <c r="N110" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="O110" s="2"/>
+      <c r="O110" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P110" t="s" s="2">
         <v>78</v>
       </c>
@@ -15125,7 +15087,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>118</v>
+        <v>580</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15146,7 +15108,7 @@
         <v>78</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>78</v>
@@ -15157,46 +15119,42 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>585</v>
+        <v>603</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>585</v>
+        <v>603</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>586</v>
+        <v>78</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>587</v>
+        <v>604</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>605</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>78</v>
       </c>
@@ -15244,19 +15202,19 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>589</v>
+        <v>603</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>78</v>
@@ -15265,7 +15223,7 @@
         <v>78</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>204</v>
+        <v>108</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>78</v>
@@ -15276,10 +15234,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15290,7 +15248,7 @@
         <v>79</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>78</v>
@@ -15302,13 +15260,13 @@
         <v>78</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>181</v>
+        <v>299</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>591</v>
+        <v>607</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>592</v>
+        <v>608</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15335,13 +15293,13 @@
         <v>78</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>259</v>
+        <v>78</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>593</v>
+        <v>78</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>594</v>
+        <v>78</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>78</v>
@@ -15359,13 +15317,13 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>78</v>
@@ -15380,7 +15338,7 @@
         <v>78</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>78</v>
@@ -15389,12 +15347,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
-        <v>595</v>
+        <v>609</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>595</v>
+        <v>609</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15405,10 +15363,10 @@
         <v>79</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>78</v>
@@ -15417,13 +15375,13 @@
         <v>78</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>329</v>
+        <v>104</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>596</v>
+        <v>610</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>597</v>
+        <v>611</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -15474,7 +15432,7 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>595</v>
+        <v>609</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15495,7 +15453,7 @@
         <v>78</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>78</v>
@@ -15504,12 +15462,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="114" hidden="true">
+    <row r="114">
       <c r="A114" t="s" s="2">
-        <v>598</v>
+        <v>612</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>598</v>
+        <v>612</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15520,10 +15478,10 @@
         <v>79</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>78</v>
@@ -15532,18 +15490,18 @@
         <v>78</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>599</v>
+        <v>613</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>600</v>
+        <v>614</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="O114" s="2"/>
+        <v>615</v>
+      </c>
+      <c r="N114" s="2"/>
+      <c r="O114" t="s" s="2">
+        <v>616</v>
+      </c>
       <c r="P114" t="s" s="2">
         <v>78</v>
       </c>
@@ -15591,13 +15549,13 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>598</v>
+        <v>612</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>78</v>
@@ -15612,1062 +15570,17 @@
         <v>78</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>582</v>
+        <v>108</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="115" hidden="true">
-      <c r="A115" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="C115" s="2"/>
-      <c r="D115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E115" s="2"/>
-      <c r="F115" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G115" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K115" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="O115" s="2"/>
-      <c r="P115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q115" s="2"/>
-      <c r="R115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AG115" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH115" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ115" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM115" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO115" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="C116" s="2"/>
-      <c r="D116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E116" s="2"/>
-      <c r="F116" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G116" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H116" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K116" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="L116" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
-      <c r="P116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q116" s="2"/>
-      <c r="R116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="AG116" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="AN116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO116" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="117" hidden="true">
-      <c r="A117" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="C117" s="2"/>
-      <c r="D117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E117" s="2"/>
-      <c r="F117" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G117" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K117" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
-      <c r="P117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q117" s="2"/>
-      <c r="R117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AG117" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH117" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO117" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="118" hidden="true">
-      <c r="A118" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="E118" s="2"/>
-      <c r="F118" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K118" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O118" s="2"/>
-      <c r="P118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q118" s="2"/>
-      <c r="R118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ118" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM118" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO118" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="119" hidden="true">
-      <c r="A119" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="C119" s="2"/>
-      <c r="D119" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="E119" s="2"/>
-      <c r="F119" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I119" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K119" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L119" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="P119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q119" s="2"/>
-      <c r="R119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF119" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM119" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AN119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO119" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="120" hidden="true">
-      <c r="A120" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="C120" s="2"/>
-      <c r="D120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E120" s="2"/>
-      <c r="F120" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G120" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K120" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L120" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="N120" s="2"/>
-      <c r="O120" s="2"/>
-      <c r="P120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q120" s="2"/>
-      <c r="R120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="AG120" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH120" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ120" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM120" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO120" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="121" hidden="true">
-      <c r="A121" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="C121" s="2"/>
-      <c r="D121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E121" s="2"/>
-      <c r="F121" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G121" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K121" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="L121" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
-      <c r="P121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q121" s="2"/>
-      <c r="R121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM121" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO121" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="N122" s="2"/>
-      <c r="O122" s="2"/>
-      <c r="P122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO122" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E123" s="2"/>
-      <c r="F123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="N123" s="2"/>
-      <c r="O123" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="P123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO123" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO123">
+  <autoFilter ref="A1:AO114">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16677,7 +15590,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI122">
+  <conditionalFormatting sqref="A2:AI113">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
